--- a/data/satisfaction_detail/2026/1-8月/游客.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/游客.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.93</v>
+        <v>9.930246913580246</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.99</v>
+        <v>9.990246913580247</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.98</v>
+        <v>9.972839506172839</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.99</v>
+        <v>9.989506172839505</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.93</v>
+        <v>9.866406249999999</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.917777777777777</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.925185185185185</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.99</v>
+        <v>9.994444444444444</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.883456790123457</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9.98</v>
+        <v>9.988888888888889</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.9</v>
+        <v>9.919382716049382</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.99</v>
+        <v>9.994444444444444</v>
       </c>
     </row>
     <row r="13">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.75</v>
+        <v>9.789876543209877</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.981481481481481</v>
       </c>
     </row>
     <row r="15">
